--- a/data/Klausurziele.xlsx
+++ b/data/Klausurziele.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Grundlagen EmpSoz\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E86ACE-C376-46A6-825F-9801B50FD081}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE0DFB46-7C37-4752-8749-0E3B7582AA48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12750" xr2:uid="{E625999C-AD9E-4A56-968E-439B39303E47}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12390" xr2:uid="{E625999C-AD9E-4A56-968E-439B39303E47}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
